--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Август 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Август 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92555490595</v>
+        <v>46157.93112763635</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Август 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Август 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93112763635</v>
+        <v>46157.93136777389</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Август 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Август 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93136777389</v>
+        <v>46157.9338414001</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Август 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Август 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9338414001</v>
+        <v>46157.93695941695</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Август 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Август 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93695941695</v>
+        <v>46158.28205025107</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Август 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Август 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28205025107</v>
+        <v>46158.29652491807</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Август 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Август 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29652491807</v>
+        <v>46158.29807614585</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Август 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Август 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29807614585</v>
+        <v>46158.33370549771</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Август 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Август 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33370549771</v>
+        <v>46158.37221831861</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Август 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Август 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37221831861</v>
+        <v>46158.3727568098</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
